--- a/public/exports-from-60-with-coowners/29189439.xlsx
+++ b/public/exports-from-60-with-coowners/29189439.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189439.xlsx
+++ b/public/exports-from-60-with-coowners/29189439.xlsx
@@ -9491,7 +9491,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjortdalvej 148</t>
+          <t xml:space="preserve">Klim Strandvej 11</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">3387991</t>
+          <t xml:space="preserve">3388939</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -9510,11 +9510,11 @@
         </is>
       </c>
       <c r="J127">
-        <v>1013</v>
+        <v>1989</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045365</t>
+          <t xml:space="preserve">200045366</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9566,17 +9566,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klim Strandvej 11</t>
+          <t xml:space="preserve">Peter Løthsvej 3</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">3388939</t>
+          <t xml:space="preserve">3257747</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -9585,16 +9585,16 @@
         </is>
       </c>
       <c r="J128">
-        <v>1989</v>
+        <v>2892</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045366</t>
+          <t xml:space="preserve">200045370</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -9641,17 +9641,17 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peter Løthsvej 3</t>
+          <t xml:space="preserve">Borups Alle 8</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">3257747</t>
+          <t xml:space="preserve">3391975</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -9660,11 +9660,11 @@
         </is>
       </c>
       <c r="J129">
-        <v>2892</v>
+        <v>5609</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045370</t>
+          <t xml:space="preserve">200045631</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-08</t>
+          <t xml:space="preserve">2021-02-15</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borups Alle 8</t>
+          <t xml:space="preserve">Aggersundvej 31</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">3391975</t>
+          <t xml:space="preserve">389895</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -9735,11 +9735,11 @@
         </is>
       </c>
       <c r="J130">
-        <v>5609</v>
+        <v>4258</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045631</t>
+          <t xml:space="preserve">200046144</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-15</t>
+          <t xml:space="preserve">2021-02-25</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9806,15 +9806,15 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J131">
-        <v>4258</v>
+        <v>2413</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046144</t>
+          <t xml:space="preserve">200046145</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aggersundvej 31</t>
+          <t xml:space="preserve">Skolevænget 3</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9876,20 +9876,20 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">389895</t>
+          <t xml:space="preserve">3245971</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J132">
-        <v>2413</v>
+        <v>2037</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046145</t>
+          <t xml:space="preserve">200047894</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-25</t>
+          <t xml:space="preserve">2021-04-11</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 3</t>
+          <t xml:space="preserve">Aggersundvej 3</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">3245971</t>
+          <t xml:space="preserve">389900, 389901</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -9960,11 +9960,11 @@
         </is>
       </c>
       <c r="J133">
-        <v>2037</v>
+        <v>5756</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047894</t>
+          <t xml:space="preserve">200047945</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-11</t>
+          <t xml:space="preserve">2021-04-12</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aggersundvej 3</t>
+          <t xml:space="preserve">Tjørnevej 9</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10026,20 +10026,20 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">389900, 389901</t>
+          <t xml:space="preserve">3391975</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J134">
-        <v>5756</v>
+        <v>117</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047945</t>
+          <t xml:space="preserve">200047992</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-12</t>
+          <t xml:space="preserve">2021-04-13</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnevej 9</t>
+          <t xml:space="preserve">Parkvej 12</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -10101,20 +10101,20 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">3391975</t>
+          <t xml:space="preserve">3390622</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J135">
-        <v>117</v>
+        <v>192</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047992</t>
+          <t xml:space="preserve">200048115</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-13</t>
+          <t xml:space="preserve">2021-04-15</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10166,17 +10166,17 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 12</t>
+          <t xml:space="preserve">Skolevej 5</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">3390622</t>
+          <t xml:space="preserve">3242263</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -10185,21 +10185,21 @@
         </is>
       </c>
       <c r="J136">
-        <v>192</v>
+        <v>1800</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">200048115</t>
+          <t xml:space="preserve">311139958</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+          <t xml:space="preserve">Dansk Infrarød Inspektion A/S</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-15</t>
+          <t xml:space="preserve">2025-10-13</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10256,11 +10256,11 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J137">
-        <v>1800</v>
+        <v>1220</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -10331,11 +10331,11 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J138">
-        <v>1220</v>
+        <v>679</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -10406,11 +10406,11 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J139">
-        <v>679</v>
+        <v>140</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -10481,11 +10481,11 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J140">
-        <v>140</v>
+        <v>4300</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -10556,11 +10556,11 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J141">
-        <v>4300</v>
+        <v>2004</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -10616,40 +10616,40 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 5</t>
+          <t xml:space="preserve">Skolegade 6</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242263</t>
+          <t xml:space="preserve">3231236</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J142">
-        <v>2004</v>
+        <v>449</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311139958</t>
+          <t xml:space="preserve">311141837</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Infrarød Inspektion A/S</t>
+          <t xml:space="preserve">JPH Energi A/S</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-13</t>
+          <t xml:space="preserve">2025-10-26</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10691,40 +10691,40 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 6</t>
+          <t xml:space="preserve">Assenbækvej 2</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9700</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">3231236</t>
+          <t xml:space="preserve">3240143</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J143">
-        <v>449</v>
+        <v>772</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311141837</t>
+          <t xml:space="preserve">311146695</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t xml:space="preserve">JPH Energi A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-26</t>
+          <t xml:space="preserve">2025-11-23</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,17 +10766,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assenbækvej 2</t>
+          <t xml:space="preserve">Blokhusvej 41</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9700</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">3240143</t>
+          <t xml:space="preserve">3232158</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -10785,11 +10785,11 @@
         </is>
       </c>
       <c r="J144">
-        <v>772</v>
+        <v>4595</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311146695</t>
+          <t xml:space="preserve">311147290</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-23</t>
+          <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blokhusvej 41</t>
+          <t xml:space="preserve">Blokhusvej 43</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -10856,11 +10856,11 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J145">
-        <v>4595</v>
+        <v>1014</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blokhusvej 43</t>
+          <t xml:space="preserve">Bredgade 101</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10926,25 +10926,25 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">3232158</t>
+          <t xml:space="preserve">3231646</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J146">
-        <v>1014</v>
+        <v>4245</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147290</t>
+          <t xml:space="preserve">311147235</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">JPH Energi A/S</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -10991,17 +10991,17 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 101</t>
+          <t xml:space="preserve">Gerdsvej 1</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9700</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">3231646</t>
+          <t xml:space="preserve">3239962</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -11010,16 +11010,16 @@
         </is>
       </c>
       <c r="J147">
-        <v>4245</v>
+        <v>2045</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147235</t>
+          <t xml:space="preserve">311147288</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t xml:space="preserve">JPH Energi A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -11066,17 +11066,17 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerdsvej 1</t>
+          <t xml:space="preserve">Lundbakvej 5</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">9700</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">3239962</t>
+          <t xml:space="preserve">3233529</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -11085,16 +11085,16 @@
         </is>
       </c>
       <c r="J148">
-        <v>2045</v>
+        <v>3825</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147288</t>
+          <t xml:space="preserve">311147224</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">JPH Energi A/S</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11141,17 +11141,17 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundbakvej 5</t>
+          <t xml:space="preserve">Nolsvej 1</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9493</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">3233529</t>
+          <t xml:space="preserve">7898532</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -11160,11 +11160,11 @@
         </is>
       </c>
       <c r="J149">
-        <v>3825</v>
+        <v>999</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147224</t>
+          <t xml:space="preserve">311147356</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nolsvej 1</t>
+          <t xml:space="preserve">Nolsvej 1A</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11231,15 +11231,15 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J150">
-        <v>999</v>
+        <v>1405</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147356</t>
+          <t xml:space="preserve">311147369</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nolsvej 1A</t>
+          <t xml:space="preserve">Nolsvej 3</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -11306,15 +11306,15 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J151">
-        <v>1405</v>
+        <v>488</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147369</t>
+          <t xml:space="preserve">311147367</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11366,30 +11366,30 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nolsvej 3</t>
+          <t xml:space="preserve">Skolegade 2</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">9493</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">7898532</t>
+          <t xml:space="preserve">3231236</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J152">
-        <v>488</v>
+        <v>283</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147367</t>
+          <t xml:space="preserve">311147211</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2</t>
+          <t xml:space="preserve">Skolegade 4</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11456,15 +11456,15 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J153">
-        <v>283</v>
+        <v>5012</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147211</t>
+          <t xml:space="preserve">311147212</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11531,11 +11531,11 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J154">
-        <v>5012</v>
+        <v>1840</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 4</t>
+          <t xml:space="preserve">Gammelgaardsvej 44</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11601,20 +11601,20 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">3231236</t>
+          <t xml:space="preserve">409816, 409817</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J155">
-        <v>1840</v>
+        <v>2162</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147212</t>
+          <t xml:space="preserve">311148091</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-25</t>
+          <t xml:space="preserve">2025-12-01</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11666,17 +11666,17 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammelgaardsvej 44</t>
+          <t xml:space="preserve">Skolegade 3</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">409816, 409817</t>
+          <t xml:space="preserve">3244768</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -11685,11 +11685,11 @@
         </is>
       </c>
       <c r="J156">
-        <v>2162</v>
+        <v>530</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311148091</t>
+          <t xml:space="preserve">311149340</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-01</t>
+          <t xml:space="preserve">2025-12-08</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11756,11 +11756,11 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J157">
-        <v>530</v>
+        <v>1424</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -11816,30 +11816,30 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 3</t>
+          <t xml:space="preserve">Præstegaardsvej 26A</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">3244768</t>
+          <t xml:space="preserve">3227505</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J158">
-        <v>1424</v>
+        <v>995</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311149340</t>
+          <t xml:space="preserve">311161159</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-08</t>
+          <t xml:space="preserve">2026-02-26</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11906,11 +11906,11 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J159">
-        <v>995</v>
+        <v>236</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -11966,30 +11966,30 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstegaardsvej 26A</t>
+          <t xml:space="preserve">Thomasmindeparken 1</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">3227505</t>
+          <t xml:space="preserve">8369908</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J160">
-        <v>236</v>
+        <v>383</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311161159</t>
+          <t xml:space="preserve">311163902</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-26</t>
+          <t xml:space="preserve">2026-03-11</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomasmindeparken 1</t>
+          <t xml:space="preserve">Sundbyvej 30</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">8369908</t>
+          <t xml:space="preserve">3262677</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -12060,11 +12060,11 @@
         </is>
       </c>
       <c r="J161">
-        <v>383</v>
+        <v>799</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311163902</t>
+          <t xml:space="preserve">311166177</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-11</t>
+          <t xml:space="preserve">2026-03-21</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12116,17 +12116,17 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sundbyvej 30</t>
+          <t xml:space="preserve">Lundbakvej 1D</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">3262677</t>
+          <t xml:space="preserve">3233518</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -12135,21 +12135,21 @@
         </is>
       </c>
       <c r="J162">
-        <v>799</v>
+        <v>434</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311166177</t>
+          <t xml:space="preserve">311168491</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve">JPH Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-21</t>
+          <t xml:space="preserve">2026-04-05</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12191,17 +12191,17 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundbakvej 1D</t>
+          <t xml:space="preserve">Hjorthsvej 7</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">3233518</t>
+          <t xml:space="preserve">3239175</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -12210,21 +12210,21 @@
         </is>
       </c>
       <c r="J163">
-        <v>434</v>
+        <v>487</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311168491</t>
+          <t xml:space="preserve">311169236</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">JPH Energi A/S</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-05</t>
+          <t xml:space="preserve">2026-04-08</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjorthsvej 7</t>
+          <t xml:space="preserve">Peter Løthsvej 10</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">3239175</t>
+          <t xml:space="preserve">7752709</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -12285,11 +12285,11 @@
         </is>
       </c>
       <c r="J164">
-        <v>487</v>
+        <v>912</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311169236</t>
+          <t xml:space="preserve">311171770</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-08</t>
+          <t xml:space="preserve">2026-04-20</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peter Løthsvej 10</t>
+          <t xml:space="preserve">Aaby Sdr. Gade 35</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">7752709</t>
+          <t xml:space="preserve">9134559</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -12360,21 +12360,21 @@
         </is>
       </c>
       <c r="J165">
-        <v>912</v>
+        <v>5565</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311171770</t>
+          <t xml:space="preserve">311172317</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t xml:space="preserve">JPH Energi A/S</t>
+          <t xml:space="preserve">Dansk Infrarød Inspektion A/S</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-20</t>
+          <t xml:space="preserve">2026-04-24</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaby Sdr. Gade 35</t>
+          <t xml:space="preserve">Kattedamsvej 26</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">9134559</t>
+          <t xml:space="preserve">3258634</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -12435,11 +12435,11 @@
         </is>
       </c>
       <c r="J166">
-        <v>5565</v>
+        <v>8065</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311172317</t>
+          <t xml:space="preserve">311178208</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-24</t>
+          <t xml:space="preserve">2026-05-23</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kattedamsvej 26</t>
+          <t xml:space="preserve">Kattedamsvej 34</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12506,11 +12506,11 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J167">
-        <v>8065</v>
+        <v>289</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
@@ -12566,40 +12566,40 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kattedamsvej 34</t>
+          <t xml:space="preserve">Gustav Zimmersvej 29</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9430</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258634</t>
+          <t xml:space="preserve">1413132</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J168">
-        <v>289</v>
+        <v>1888</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311178208</t>
+          <t xml:space="preserve">311179271</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Infrarød Inspektion A/S</t>
+          <t xml:space="preserve">JPH Energi A/S</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-23</t>
+          <t xml:space="preserve">2026-05-27</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12656,11 +12656,11 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J169">
-        <v>1888</v>
+        <v>281</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -12716,30 +12716,30 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gustav Zimmersvej 29</t>
+          <t xml:space="preserve">Birkevangen 4</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">9430</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1413132</t>
+          <t xml:space="preserve">7584516</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J170">
-        <v>281</v>
+        <v>1115</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311179271</t>
+          <t xml:space="preserve">311179947</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-27</t>
+          <t xml:space="preserve">2026-05-31</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevangen 4</t>
+          <t xml:space="preserve">Gl. Landevej 62C</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">7584516</t>
+          <t xml:space="preserve">3239487</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -12810,11 +12810,11 @@
         </is>
       </c>
       <c r="J171">
-        <v>1115</v>
+        <v>1164</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311179947</t>
+          <t xml:space="preserve">311181752</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-31</t>
+          <t xml:space="preserve">2026-06-08</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12881,11 +12881,11 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J172">
-        <v>1164</v>
+        <v>176</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Landevej 62C</t>
+          <t xml:space="preserve">Idrætsvej 15A</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12951,7 +12951,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">3239487</t>
+          <t xml:space="preserve">3262653</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -12960,11 +12960,11 @@
         </is>
       </c>
       <c r="J173">
-        <v>176</v>
+        <v>1113</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311181752</t>
+          <t xml:space="preserve">311181777</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 15A</t>
+          <t xml:space="preserve">Gl. Landevej 68</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">3262653</t>
+          <t xml:space="preserve">7232348</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -13035,11 +13035,11 @@
         </is>
       </c>
       <c r="J174">
-        <v>1113</v>
+        <v>112</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311181777</t>
+          <t xml:space="preserve">311185935</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-08</t>
+          <t xml:space="preserve">2026-06-27</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13106,11 +13106,11 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J175">
-        <v>112</v>
+        <v>189</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
@@ -13166,30 +13166,30 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Landevej 68</t>
+          <t xml:space="preserve">Blokhusvej 47A</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">7232348</t>
+          <t xml:space="preserve">3232158</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J176">
-        <v>189</v>
+        <v>428</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311185935</t>
+          <t xml:space="preserve">311190610</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-27</t>
+          <t xml:space="preserve">2026-07-18</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blokhusvej 47A</t>
+          <t xml:space="preserve">Stadionvej 7</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -13251,20 +13251,20 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">3232158</t>
+          <t xml:space="preserve">3234526</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J177">
-        <v>428</v>
+        <v>249</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311190610</t>
+          <t xml:space="preserve">311204585</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13274,17 +13274,17 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-18</t>
+          <t xml:space="preserve">2026-10-05</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -13331,11 +13331,11 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J178">
-        <v>249</v>
+        <v>129</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
@@ -13391,30 +13391,30 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 7</t>
+          <t xml:space="preserve">Elmevej 6</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">3234526</t>
+          <t xml:space="preserve">3242523</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J179">
-        <v>129</v>
+        <v>572</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311204585</t>
+          <t xml:space="preserve">311207345</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-05</t>
+          <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmevej 6</t>
+          <t xml:space="preserve">Tjørnevænget 1</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242523</t>
+          <t xml:space="preserve">3243120</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -13485,11 +13485,11 @@
         </is>
       </c>
       <c r="J180">
-        <v>572</v>
+        <v>319</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207345</t>
+          <t xml:space="preserve">311209474</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13499,7 +13499,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnevænget 1</t>
+          <t xml:space="preserve">Rotfelds Vej 11</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">3243120</t>
+          <t xml:space="preserve">3242161</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -13560,11 +13560,11 @@
         </is>
       </c>
       <c r="J181">
-        <v>319</v>
+        <v>840</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311209474</t>
+          <t xml:space="preserve">311210030</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-31</t>
+          <t xml:space="preserve">2026-11-02</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13616,17 +13616,17 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotfelds Vej 11</t>
+          <t xml:space="preserve">Vester Fælledvej 17</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242161</t>
+          <t xml:space="preserve">3391896</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -13635,11 +13635,11 @@
         </is>
       </c>
       <c r="J182">
-        <v>840</v>
+        <v>635</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210030</t>
+          <t xml:space="preserve">311210142</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vester Fælledvej 17</t>
+          <t xml:space="preserve">Svinkløvvej 1</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">3391896</t>
+          <t xml:space="preserve">8826071</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -13710,11 +13710,11 @@
         </is>
       </c>
       <c r="J183">
-        <v>635</v>
+        <v>575</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210142</t>
+          <t xml:space="preserve">311210311</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-02</t>
+          <t xml:space="preserve">2026-11-03</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13766,17 +13766,17 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svinkløvvej 1</t>
+          <t xml:space="preserve">Viaduktvej 28A</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">8826071</t>
+          <t xml:space="preserve">3257468</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -13785,11 +13785,11 @@
         </is>
       </c>
       <c r="J184">
-        <v>575</v>
+        <v>491</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210311</t>
+          <t xml:space="preserve">311210617</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-03</t>
+          <t xml:space="preserve">2026-11-04</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viaduktvej 28A</t>
+          <t xml:space="preserve">Skipper Clements Vej 25</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">3257468</t>
+          <t xml:space="preserve">3258602</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -13860,11 +13860,11 @@
         </is>
       </c>
       <c r="J185">
-        <v>491</v>
+        <v>747</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210617</t>
+          <t xml:space="preserve">311212446</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-04</t>
+          <t xml:space="preserve">2026-11-15</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skipper Clements Vej 25</t>
+          <t xml:space="preserve">Anlægsvej 1</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -13926,7 +13926,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258602</t>
+          <t xml:space="preserve">3258842</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -13935,11 +13935,11 @@
         </is>
       </c>
       <c r="J186">
-        <v>747</v>
+        <v>537</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212446</t>
+          <t xml:space="preserve">311212700</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-15</t>
+          <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anlægsvej 1</t>
+          <t xml:space="preserve">Rønnebærvej 8</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -14001,7 +14001,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258842</t>
+          <t xml:space="preserve">3221223</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -14010,11 +14010,11 @@
         </is>
       </c>
       <c r="J187">
-        <v>537</v>
+        <v>1422</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212700</t>
+          <t xml:space="preserve">311213714</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-16</t>
+          <t xml:space="preserve">2026-11-22</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14066,30 +14066,30 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønnebærvej 8</t>
+          <t xml:space="preserve">Ørebrovej 128</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">3221223</t>
+          <t xml:space="preserve">9009874</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J188">
-        <v>1422</v>
+        <v>557</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311213714</t>
+          <t xml:space="preserve">311213892</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-22</t>
+          <t xml:space="preserve">2026-11-23</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14156,15 +14156,15 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J189">
-        <v>557</v>
+        <v>3128</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311213892</t>
+          <t xml:space="preserve">311214103</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-23</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørebrovej 128</t>
+          <t xml:space="preserve">Parkvænget 27</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -14226,20 +14226,20 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">9009874</t>
+          <t xml:space="preserve">389901</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J190">
-        <v>3128</v>
+        <v>294</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214103</t>
+          <t xml:space="preserve">311225294</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14291,30 +14291,30 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørtorupvej 2</t>
+          <t xml:space="preserve">Bøge Bakker 7</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">3387991</t>
+          <t xml:space="preserve">8275117</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J191">
-        <v>422</v>
+        <v>327</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223668</t>
+          <t xml:space="preserve">311226665</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14324,7 +14324,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-20</t>
+          <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14366,30 +14366,30 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvænget 27</t>
+          <t xml:space="preserve">Kordalsvej 13</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9493</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">389901</t>
+          <t xml:space="preserve">3235639</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J192">
-        <v>294</v>
+        <v>396</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225294</t>
+          <t xml:space="preserve">311226663</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-30</t>
+          <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøge Bakker 7</t>
+          <t xml:space="preserve">Niels Juels Vej 1</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -14451,7 +14451,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">8275117</t>
+          <t xml:space="preserve">7986826</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -14460,11 +14460,11 @@
         </is>
       </c>
       <c r="J193">
-        <v>327</v>
+        <v>436</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226665</t>
+          <t xml:space="preserve">311229952</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-06</t>
+          <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14516,30 +14516,30 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kordalsvej 13</t>
+          <t xml:space="preserve">Østmarken 2</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">9493</t>
+          <t xml:space="preserve">9430</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">3235639</t>
+          <t xml:space="preserve">7313030</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J194">
-        <v>396</v>
+        <v>944</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226663</t>
+          <t xml:space="preserve">311236277</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-06</t>
+          <t xml:space="preserve">2027-03-23</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14591,30 +14591,30 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Juels Vej 1</t>
+          <t xml:space="preserve">Præstegaardsvej 26C</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">7986826</t>
+          <t xml:space="preserve">3227505</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J195">
-        <v>436</v>
+        <v>296</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229952</t>
+          <t xml:space="preserve">311430960</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14624,7 +14624,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-22</t>
+          <t xml:space="preserve">2030-03-31</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14666,30 +14666,30 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østmarken 2</t>
+          <t xml:space="preserve">Præstegaardsvej 34</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">9430</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">7313030</t>
+          <t xml:space="preserve">3227457</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J196">
-        <v>944</v>
+        <v>519</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236277</t>
+          <t xml:space="preserve">311430955</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-23</t>
+          <t xml:space="preserve">2030-03-31</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14741,40 +14741,40 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstegaardsvej 26C</t>
+          <t xml:space="preserve">Mågevej 19</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">3227505</t>
+          <t xml:space="preserve">3391352</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J197">
-        <v>296</v>
+        <v>237</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311430960</t>
+          <t xml:space="preserve">311483905</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t xml:space="preserve">JPH Energi A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-31</t>
+          <t xml:space="preserve">2030-12-18</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14816,17 +14816,17 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstegaardsvej 34</t>
+          <t xml:space="preserve">Stationsvej 20</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">3227457</t>
+          <t xml:space="preserve">3242155</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -14835,21 +14835,21 @@
         </is>
       </c>
       <c r="J198">
-        <v>519</v>
+        <v>2615</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311430955</t>
+          <t xml:space="preserve">311502859</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t xml:space="preserve">JPH Energi A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-31</t>
+          <t xml:space="preserve">2031-03-12</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14876,12 +14876,12 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jammerbugt Kommune</t>
+          <t xml:space="preserve">NØRRESUNDBY BOLIGSELSKAB</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -14891,17 +14891,17 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mågevej 19</t>
+          <t xml:space="preserve">Nolsvej 10</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9493</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">3391352</t>
+          <t xml:space="preserve">411987, 411988</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -14910,21 +14910,21 @@
         </is>
       </c>
       <c r="J199">
-        <v>237</v>
+        <v>2824</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483905</t>
+          <t xml:space="preserve">311584806</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-18</t>
+          <t xml:space="preserve">2032-03-14</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14951,12 +14951,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jammerbugt Kommune</t>
+          <t xml:space="preserve">HF&amp;VUC NORD S/I</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -14966,17 +14966,17 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 20</t>
+          <t xml:space="preserve">Teknologiparken 1A</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242155</t>
+          <t xml:space="preserve">392195, 392196</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -14985,11 +14985,11 @@
         </is>
       </c>
       <c r="J200">
-        <v>2615</v>
+        <v>718</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311502859</t>
+          <t xml:space="preserve">311653716</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-12</t>
+          <t xml:space="preserve">2033-01-12</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15026,12 +15026,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">NØRRESUNDBY BOLIGSELSKAB</t>
+          <t xml:space="preserve">Jammerbugt Kommune</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -15041,17 +15041,17 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nolsvej 10</t>
+          <t xml:space="preserve">Jens Møllersvej 3</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">9493</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">411987, 411988</t>
+          <t xml:space="preserve">3258795</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -15060,21 +15060,21 @@
         </is>
       </c>
       <c r="J201">
-        <v>2824</v>
+        <v>7053</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584806</t>
+          <t xml:space="preserve">311680518</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve">Preben Dam ApS</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-14</t>
+          <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">HF&amp;VUC NORD S/I</t>
+          <t xml:space="preserve">Jammerbugt Kommune</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teknologiparken 1A</t>
+          <t xml:space="preserve">Jens Møllersvej 3</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -15126,30 +15126,30 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">392195, 392196</t>
+          <t xml:space="preserve">3258795</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J202">
-        <v>718</v>
+        <v>1233</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653716</t>
+          <t xml:space="preserve">311680518</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">Preben Dam ApS</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-12</t>
+          <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -15206,11 +15206,11 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J203">
-        <v>7053</v>
+        <v>413</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
@@ -15266,40 +15266,40 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jens Møllersvej 3</t>
+          <t xml:space="preserve">Jetsmark Kirkevej 5</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258795</t>
+          <t xml:space="preserve">100246402</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J204">
-        <v>1233</v>
+        <v>8883</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680518</t>
+          <t xml:space="preserve">311687096</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preben Dam ApS</t>
+          <t xml:space="preserve">Komplet Rådgivning IVS</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-12</t>
+          <t xml:space="preserve">2033-06-12</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -15341,40 +15341,40 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jens Møllersvej 3</t>
+          <t xml:space="preserve">Possementmagervej 1</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258795</t>
+          <t xml:space="preserve">3231805</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J205">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680518</t>
+          <t xml:space="preserve">311788173</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preben Dam ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-12</t>
+          <t xml:space="preserve">2034-09-29</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -15416,17 +15416,17 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jetsmark Kirkevej 5</t>
+          <t xml:space="preserve">Rønnebærvej 12A</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">100246402</t>
+          <t xml:space="preserve">3221313</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -15435,21 +15435,21 @@
         </is>
       </c>
       <c r="J206">
-        <v>8883</v>
+        <v>1423</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311687096</t>
+          <t xml:space="preserve">311853697</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Komplet Rådgivning IVS</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-12</t>
+          <t xml:space="preserve">2035-09-04</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -15476,12 +15476,12 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jammerbugt Kommune</t>
+          <t xml:space="preserve">MICA NORD ApS</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -15491,17 +15491,17 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Possementmagervej 1</t>
+          <t xml:space="preserve">Kirkegade 1</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">3231805</t>
+          <t xml:space="preserve">389861, 389865, 389866, 389862, 389863, 389864, 389867, 389869, 389870, 389871, 389872, 389868</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -15510,21 +15510,21 @@
         </is>
       </c>
       <c r="J207">
-        <v>410</v>
+        <v>2387</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311788173</t>
+          <t xml:space="preserve">311873285</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-29</t>
+          <t xml:space="preserve">2035-12-12</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15566,17 +15566,17 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønnebærvej 12A</t>
+          <t xml:space="preserve">Strandvejen 143A</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">3221313</t>
+          <t xml:space="preserve">8668873</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -15585,21 +15585,21 @@
         </is>
       </c>
       <c r="J208">
-        <v>1423</v>
+        <v>254</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311853697</t>
+          <t xml:space="preserve">311873714</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve">Preben Dam ApS</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-04</t>
+          <t xml:space="preserve">2035-12-16</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15626,12 +15626,12 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">MICA NORD ApS</t>
+          <t xml:space="preserve">Jammerbugt Kommune</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 1</t>
+          <t xml:space="preserve">Egevej 8</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">389861, 389865, 389866, 389862, 389863, 389864, 389867, 389869, 389870, 389871, 389872, 389868</t>
+          <t xml:space="preserve">389886, 389887, 389888</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -15660,21 +15660,21 @@
         </is>
       </c>
       <c r="J209">
-        <v>2387</v>
+        <v>2559</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873285</t>
+          <t xml:space="preserve">311888110</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-12</t>
+          <t xml:space="preserve">2036-03-17</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 143A</t>
+          <t xml:space="preserve">Parkvej 28</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -15726,30 +15726,30 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">8668873</t>
+          <t xml:space="preserve">389889, 389890, 389891, 389892, 389893, 389894</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J210">
-        <v>254</v>
+        <v>374</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873708</t>
+          <t xml:space="preserve">311888109</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-16</t>
+          <t xml:space="preserve">2036-03-17</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egevej 8</t>
+          <t xml:space="preserve">Sygehusvej 14</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -15801,7 +15801,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">389886, 389887, 389888</t>
+          <t xml:space="preserve">3243191</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -15810,21 +15810,21 @@
         </is>
       </c>
       <c r="J211">
-        <v>2559</v>
+        <v>3319</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888110</t>
+          <t xml:space="preserve">311898289</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve">Komplet Rådgivning IVS</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-17</t>
+          <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 28</t>
+          <t xml:space="preserve">Sygehusvej 6</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -15876,30 +15876,30 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">389889, 389890, 389891, 389892, 389893, 389894</t>
+          <t xml:space="preserve">3243191</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J212">
-        <v>374</v>
+        <v>1558</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888109</t>
+          <t xml:space="preserve">311898289</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve">Komplet Rådgivning IVS</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-17</t>
+          <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sygehusvej 14</t>
+          <t xml:space="preserve">Sygehusvej 6</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -15956,11 +15956,11 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J213">
-        <v>3319</v>
+        <v>78</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sygehusvej 6</t>
+          <t xml:space="preserve">Sygehusvej 6D</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -16031,11 +16031,11 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J214">
-        <v>1558</v>
+        <v>178</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sygehusvej 6</t>
+          <t xml:space="preserve">Vestergade 9</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -16101,30 +16101,30 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">3243191</t>
+          <t xml:space="preserve">389878</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J215">
-        <v>78</v>
+        <v>1788</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898289</t>
+          <t xml:space="preserve">311901807</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Komplet Rådgivning IVS</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-01</t>
+          <t xml:space="preserve">2036-05-18</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -16166,40 +16166,40 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sygehusvej 6D</t>
+          <t xml:space="preserve">Kattedamsvej 32B</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">3243191</t>
+          <t xml:space="preserve">3258634</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J216">
-        <v>178</v>
+        <v>1552</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898289</t>
+          <t xml:space="preserve">311902872</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Komplet Rådgivning IVS</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-01</t>
+          <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -16241,30 +16241,30 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 9</t>
+          <t xml:space="preserve">Nørtorupvej 2</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">389878</t>
+          <t xml:space="preserve">3387991</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J217">
-        <v>1788</v>
+        <v>422</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311901807</t>
+          <t xml:space="preserve">311926435</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-18</t>
+          <t xml:space="preserve">2036-09-17</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -16316,40 +16316,40 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kattedamsvej 32B</t>
+          <t xml:space="preserve">Hjortdalvej 148</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258634</t>
+          <t xml:space="preserve">3387991</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J218">
-        <v>1552</v>
+        <v>1013</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311902872</t>
+          <t xml:space="preserve">311927258</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artelia A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-21</t>
+          <t xml:space="preserve">2036-09-22</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189439.xlsx
+++ b/public/exports-from-60-with-coowners/29189439.xlsx
@@ -13279,12 +13279,12 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -13354,12 +13354,12 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -13429,12 +13429,12 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -15589,12 +15589,12 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873714</t>
+          <t xml:space="preserve">311873708</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preben Dam ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M208" t="inlineStr">
